--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1440-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1440-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C743C9F5-ED64-4C35-BE72-7C45B96F350A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{371F2032-B9EF-4560-BBC8-F3DFADE49A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{74642197-95D4-4824-BBB8-700FF091A879}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{43EB4E4F-24BC-461D-B6CF-61CDF3493F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="1440-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,28 +1490,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97FA13F-FC23-4202-B582-6679F701A382}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE8F0AC-C80F-4561-8472-BF05537E5B06}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1544,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1581,7 +1580,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1633,7 +1632,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1701,7 +1700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1773,7 +1772,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1845,7 +1844,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2061,7 +2060,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2133,7 +2132,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2205,7 +2204,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2277,7 +2276,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2421,7 +2420,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2493,7 +2492,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2709,7 +2708,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2781,7 +2780,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3069,7 +3068,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3141,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3429,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3501,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3573,7 +3572,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3717,7 +3716,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3789,7 +3788,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3861,7 +3860,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3933,7 +3932,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -4005,7 +4004,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4077,7 +4076,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4149,7 +4148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1990</v>
       </c>
@@ -4221,7 +4220,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1989</v>
       </c>
@@ -4293,7 +4292,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>1988</v>
       </c>
@@ -4365,7 +4364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1987</v>
       </c>
@@ -4437,7 +4436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="34">
         <v>1986</v>
       </c>
@@ -4509,7 +4508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1984</v>
       </c>
@@ -4581,7 +4580,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="34" t="s">
         <v>55</v>
       </c>
